--- a/data/trans_dic/P3A$yo-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A$yo-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,65; 67,38</t>
+          <t>58,56; 67,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92,02; 95,48</t>
+          <t>91,94; 95,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,72; 82,47</t>
+          <t>76,71; 82,2</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,0; 66,51</t>
+          <t>24,87; 66,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,13; 93,76</t>
+          <t>90,28; 93,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,58; 79,41</t>
+          <t>47,28; 79,42</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,63; 72,01</t>
+          <t>63,45; 71,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,94; 96,42</t>
+          <t>90,3; 96,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,87; 88,34</t>
+          <t>78,69; 88,24</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>63,75; 70,57</t>
+          <t>63,59; 70,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,78; 90,8</t>
+          <t>85,57; 90,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,27; 81,34</t>
+          <t>76,36; 81,34</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,57; 66,49</t>
+          <t>46,73; 66,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,35; 93,16</t>
+          <t>90,37; 93,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67,01; 80,34</t>
+          <t>68,12; 80,32</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>372385; 427817</t>
+          <t>371840; 428157</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>667438; 692558</t>
+          <t>666884; 692062</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1043579; 1121855</t>
+          <t>1043492; 1118120</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>333978; 793333</t>
+          <t>296623; 791176</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>864063; 898875</t>
+          <t>865503; 898428</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1023615; 1708519</t>
+          <t>1017286; 1708633</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>448385; 507459</t>
+          <t>447112; 507257</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>839449; 899971</t>
+          <t>842797; 904586</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1291978; 1447117</t>
+          <t>1289041; 1445410</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>590454; 653645</t>
+          <t>588974; 652798</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>938175; 993110</t>
+          <t>935813; 990670</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1540611; 1642909</t>
+          <t>1542309; 1643001</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1645467; 2299797</t>
+          <t>1616269; 2302431</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3352739; 3457073</t>
+          <t>3353826; 3455773</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4804174; 5760368</t>
+          <t>4883769; 5758566</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$yo-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A$yo-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,56; 67,43</t>
+          <t>58,57; 66,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,94; 95,41</t>
+          <t>91,23; 94,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,71; 82,2</t>
+          <t>75,73; 80,65</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,87; 66,33</t>
+          <t>61,44; 68,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,28; 93,72</t>
+          <t>89,91; 93,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,28; 79,42</t>
+          <t>76,62; 80,47</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,45; 71,98</t>
+          <t>63,65; 71,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,3; 96,92</t>
+          <t>87,92; 92,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,69; 88,24</t>
+          <t>76,5; 81,56</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>63,59; 70,48</t>
+          <t>62,92; 69,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,57; 90,58</t>
+          <t>85,44; 89,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,36; 81,34</t>
+          <t>75,53; 79,34</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,73; 66,57</t>
+          <t>63,75; 67,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,37; 93,12</t>
+          <t>89,56; 91,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68,12; 80,32</t>
+          <t>77,31; 79,47</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>401782</t>
+          <t>432141</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>680879</t>
+          <t>685471</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1082661</t>
+          <t>1117612</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>371840; 428157</t>
+          <t>404275; 458547</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>666884; 692062</t>
+          <t>669777; 695963</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1043492; 1118120</t>
+          <t>1078691; 1148761</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>619109</t>
+          <t>681901</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>883438</t>
+          <t>985056</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1502548</t>
+          <t>1666957</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>296623; 791176</t>
+          <t>644439; 716147</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>865503; 898428</t>
+          <t>963321; 1002231</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1017286; 1708633</t>
+          <t>1624680; 1706175</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>477663</t>
+          <t>542863</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>870118</t>
+          <t>736714</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1347781</t>
+          <t>1279576</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>447112; 507257</t>
+          <t>511170; 572086</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>842797; 904586</t>
+          <t>714114; 754309</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1289041; 1445410</t>
+          <t>1235786; 1317392</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>622054</t>
+          <t>655652</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>963142</t>
+          <t>978683</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1585195</t>
+          <t>1634336</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>588974; 652798</t>
+          <t>622570; 685474</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>935813; 990670</t>
+          <t>955018; 1001245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1542309; 1643001</t>
+          <t>1591504; 1671898</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2120608</t>
+          <t>2312557</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3397577</t>
+          <t>3385923</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5518185</t>
+          <t>5698481</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1616269; 2302431</t>
+          <t>2251481; 2374350</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3353826; 3455773</t>
+          <t>3345644; 3421280</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4883769; 5758566</t>
+          <t>5618246; 5775071</t>
         </is>
       </c>
     </row>
